--- a/artfynd/A 34225-2026 artfynd.xlsx
+++ b/artfynd/A 34225-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193005</v>
       </c>
       <c r="B2" t="n">
-        <v>96666</v>
+        <v>96669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136193996</v>
       </c>
       <c r="B6" t="n">
-        <v>96656</v>
+        <v>96659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136193735</v>
       </c>
       <c r="B7" t="n">
-        <v>96645</v>
+        <v>96648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136193984</v>
       </c>
       <c r="B8" t="n">
-        <v>96645</v>
+        <v>96648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136193836</v>
       </c>
       <c r="B9" t="n">
-        <v>96450</v>
+        <v>96453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 34225-2026 artfynd.xlsx
+++ b/artfynd/A 34225-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193005</v>
       </c>
       <c r="B2" t="n">
-        <v>96669</v>
+        <v>96670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136193996</v>
       </c>
       <c r="B6" t="n">
-        <v>96659</v>
+        <v>96660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136193735</v>
       </c>
       <c r="B7" t="n">
-        <v>96648</v>
+        <v>96649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136193984</v>
       </c>
       <c r="B8" t="n">
-        <v>96648</v>
+        <v>96649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136193836</v>
       </c>
       <c r="B9" t="n">
-        <v>96453</v>
+        <v>96454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 34225-2026 artfynd.xlsx
+++ b/artfynd/A 34225-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193005</v>
       </c>
       <c r="B2" t="n">
-        <v>96670</v>
+        <v>96675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192933</v>
       </c>
       <c r="B3" t="n">
-        <v>77980</v>
+        <v>77982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136193523</v>
       </c>
       <c r="B4" t="n">
-        <v>81150</v>
+        <v>81152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136320537</v>
       </c>
       <c r="B5" t="n">
-        <v>81307</v>
+        <v>81309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136193996</v>
       </c>
       <c r="B6" t="n">
-        <v>96660</v>
+        <v>96665</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136193735</v>
       </c>
       <c r="B7" t="n">
-        <v>96649</v>
+        <v>96654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136193984</v>
       </c>
       <c r="B8" t="n">
-        <v>96649</v>
+        <v>96654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136193836</v>
       </c>
       <c r="B9" t="n">
-        <v>96454</v>
+        <v>96459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136125414</v>
       </c>
       <c r="B10" t="n">
-        <v>58165</v>
+        <v>58167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136125410</v>
       </c>
       <c r="B11" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136192963</v>
       </c>
       <c r="B12" t="n">
-        <v>81137</v>
+        <v>81139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34225-2026 artfynd.xlsx
+++ b/artfynd/A 34225-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136192933</v>
       </c>
       <c r="B3" t="n">
-        <v>77982</v>
+        <v>77976</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34225-2026 artfynd.xlsx
+++ b/artfynd/A 34225-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193005</v>
       </c>
       <c r="B2" t="n">
-        <v>96675</v>
+        <v>96677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136193996</v>
       </c>
       <c r="B6" t="n">
-        <v>96665</v>
+        <v>96667</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136193735</v>
       </c>
       <c r="B7" t="n">
-        <v>96654</v>
+        <v>96656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136193984</v>
       </c>
       <c r="B8" t="n">
-        <v>96654</v>
+        <v>96656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136193836</v>
       </c>
       <c r="B9" t="n">
-        <v>96459</v>
+        <v>96461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 34225-2026 artfynd.xlsx
+++ b/artfynd/A 34225-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136320537</v>
       </c>
       <c r="B5" t="n">
-        <v>81309</v>
+        <v>81313</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
